--- a/data/trending_integrated_20261007_11.xlsx
+++ b/data/trending_integrated_20261007_11.xlsx
@@ -578,10 +578,10 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
         <v>24</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26116695454</v>
+        <v>26193657844</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -619,7 +619,7 @@
         <v>2810</v>
       </c>
       <c r="R2" t="n">
-        <v>280000</v>
+        <v>294000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7840</v>
+        <v>16970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.15%</t>
+          <t>'+14.12%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.02</v>
+        <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="H3" t="n">
-        <v>5.12</v>
+        <v>2.37</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6750</v>
+        <v>14870</v>
       </c>
       <c r="K3" t="n">
-        <v>6710</v>
+        <v>15480</v>
       </c>
       <c r="L3" t="n">
-        <v>8310</v>
+        <v>17590</v>
       </c>
       <c r="M3" t="n">
-        <v>6690</v>
+        <v>14600</v>
       </c>
       <c r="N3" t="n">
-        <v>5.14</v>
+        <v>1.39</v>
       </c>
       <c r="O3" t="n">
-        <v>50936925715</v>
+        <v>209633214760</v>
       </c>
       <c r="P3" t="n">
-        <v>23500</v>
+        <v>17590</v>
       </c>
       <c r="Q3" t="n">
-        <v>2890</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>-226000</v>
+        <v>-83000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 관련 뉴스 언급. 성수 메가프로젝트 및 건설 기초 소재 대장주로서의 위치 강조. 10만원 목표가 제시.</t>
+          <t>개인정보 유출 및 보안사고 증가 추세 속, 양자보안 기술 공급 논의 등 긍정적 뉴스에 기반한 주가 상승 전망. 주포의 물량 확보도 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '건설']</t>
+          <t>['개인정보 유출', '양자보안', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26250</v>
+        <v>26000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.38%</t>
+          <t>'+13.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H4" t="n">
         <v>2.82</v>
@@ -794,7 +794,7 @@
         <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>81847311575</v>
+        <v>84608364850</v>
       </c>
       <c r="P4" t="n">
         <v>30100</v>
@@ -803,10 +803,10 @@
         <v>11140</v>
       </c>
       <c r="R4" t="n">
-        <v>158000</v>
+        <v>223000</v>
       </c>
       <c r="S4" t="n">
-        <v>-205000</v>
+        <v>-202000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14090</v>
+        <v>7630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.27%</t>
+          <t>'+13.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.31</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="H5" t="n">
-        <v>0.79</v>
+        <v>5.12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12330</v>
+        <v>6750</v>
       </c>
       <c r="K5" t="n">
-        <v>12580</v>
+        <v>6710</v>
       </c>
       <c r="L5" t="n">
-        <v>14260</v>
+        <v>8310</v>
       </c>
       <c r="M5" t="n">
-        <v>12300</v>
+        <v>6690</v>
       </c>
       <c r="N5" t="n">
-        <v>0.48</v>
+        <v>5.14</v>
       </c>
       <c r="O5" t="n">
-        <v>133833633650</v>
+        <v>53089038200</v>
       </c>
       <c r="P5" t="n">
-        <v>20850</v>
+        <v>23500</v>
       </c>
       <c r="Q5" t="n">
-        <v>4020</v>
+        <v>2890</v>
       </c>
       <c r="R5" t="n">
-        <v>-5000</v>
+        <v>-688000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 관련 뉴스 언급. 성수 메가프로젝트 및 건설 기초 소재 대장주로서의 위치 강조. 10만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전', '납품']</t>
+          <t>['용적률', '그린벨트', '건설']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16470</v>
+        <v>13900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.76%</t>
+          <t>'+12.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14870</v>
+        <v>12330</v>
       </c>
       <c r="K6" t="n">
-        <v>15480</v>
+        <v>12580</v>
       </c>
       <c r="L6" t="n">
-        <v>17590</v>
+        <v>14260</v>
       </c>
       <c r="M6" t="n">
-        <v>14600</v>
+        <v>12300</v>
       </c>
       <c r="N6" t="n">
-        <v>1.39</v>
+        <v>0.48</v>
       </c>
       <c r="O6" t="n">
-        <v>203836055015</v>
+        <v>145041686640</v>
       </c>
       <c r="P6" t="n">
-        <v>17590</v>
+        <v>20850</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>4020</v>
       </c>
       <c r="R6" t="n">
-        <v>-91000</v>
+        <v>-65000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개인정보 유출 사고 및 국내외 보안 사고 증가에 따른 보안주로서의 부각. 양자보안 기술 공급 논의 언급.</t>
+          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', '개인정보유출']</t>
+          <t>['가스터빈', '원전', '납품']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.62%</t>
+          <t>'+10.65%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="H7" t="n">
         <v>5.01</v>
@@ -1070,7 +1070,7 @@
         <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>15345623620</v>
+        <v>15670069590</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신규 질병 확산에 따른 테마주로서의 기대감 형성. 그러나 질병의 성격(세균 vs 바이러스)에 대한 혼란 및 단타성 매매에 대한 언급.</t>
+          <t>전염병 테마주로서의 기대감과 함께, 러시아/케냐 발 질병 확산 소식에 따른 변동성 예상. 일부 부정적 분석도 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['테마주', '질병', '단타']</t>
+          <t>['전염병', '테마주', '변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.43%</t>
+          <t>'+8.81%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H8" t="n">
         <v>0.82</v>
@@ -1162,7 +1162,7 @@
         <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>8247471464</v>
+        <v>8378125429</v>
       </c>
       <c r="P8" t="n">
         <v>4760</v>
@@ -1171,7 +1171,7 @@
         <v>973</v>
       </c>
       <c r="R8" t="n">
-        <v>-43000</v>
+        <v>-31000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5370</v>
+        <v>5280</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.19%</t>
+          <t>'+5.39%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>175080778070</v>
+        <v>177858302510</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1263,23 +1263,23 @@
         <v>592</v>
       </c>
       <c r="R9" t="n">
-        <v>1405000</v>
+        <v>381000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대규모 수주 계약 임박 가능성 및 기타 법인 자사주 매집 언급. 미국 증시 호조에 따른 기대감.</t>
+          <t>기타법인 대규모 자사주 매집 및 2200억 규모 수주 계약(공시 예정) 등 구체적 근거 기반 상승 기대감. 미 증시 호조 및 JP모건 순매수도 긍정적 요인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주계약', '자사주매집', '기타법인']</t>
+          <t>['자사주 매집', '수주 계약', '기대감']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81200</v>
+        <v>271500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.18%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>247</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>140</v>
+        <v>472</v>
       </c>
       <c r="G10" t="n">
-        <v>650</v>
+        <v>1549</v>
       </c>
       <c r="H10" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K10" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L10" t="n">
-        <v>84300</v>
+        <v>279500</v>
       </c>
       <c r="M10" t="n">
-        <v>81100</v>
+        <v>268500</v>
       </c>
       <c r="N10" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>102828200950</v>
+        <v>2172546580250</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R10" t="n">
-        <v>72000</v>
+        <v>1377000</v>
       </c>
       <c r="S10" t="n">
-        <v>-40000</v>
+        <v>-5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>구글-컨스텔레이션 3.6GW 전력구매 계약 뉴스 기반 원전주 급등 기대. 웨스팅하우스 계약 체결 공시 가능성 언급.</t>
+          <t>반도체 산업 부진 및 노조 이슈 속, 기관/외인 매도세 지속. 정치적 요인에 따른 시장 불안감도 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전주', '전력구매계약', '공시']</t>
+          <t>['반도체', '노조', '외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>270750</v>
+        <v>80750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'-0.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>257</v>
       </c>
       <c r="F11" t="n">
-        <v>471</v>
+        <v>145</v>
       </c>
       <c r="G11" t="n">
-        <v>1586</v>
+        <v>662</v>
       </c>
       <c r="H11" t="n">
-        <v>46.37</v>
+        <v>22.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272000</v>
+        <v>81500</v>
       </c>
       <c r="K11" t="n">
-        <v>269500</v>
+        <v>83500</v>
       </c>
       <c r="L11" t="n">
-        <v>279500</v>
+        <v>84300</v>
       </c>
       <c r="M11" t="n">
-        <v>268500</v>
+        <v>80600</v>
       </c>
       <c r="N11" t="n">
-        <v>46.41</v>
+        <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>2083041719500</v>
+        <v>111250397300</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>90200</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>1232000</v>
+        <v>-8000</v>
       </c>
       <c r="S11" t="n">
-        <v>-121000</v>
+        <v>-36000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 및 정치적 이슈에 대한 부정적 언급 속 목표가 50만원 제시. 다만, 감정적 비난과 근거 없는 기대가 주를 이룸.</t>
+          <t>구글-컨스텔레이션 3.6GW 전력구매 계약 뉴스 기반 원전주 급등 기대. 웨스팅하우스 계약 체결 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '성과급', '목표가']</t>
+          <t>['원전주', '전력구매계약', '공시']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17590</v>
+        <v>17490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.90%</t>
+          <t>'-1.46%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1524,13 +1524,13 @@
         <v>18030</v>
       </c>
       <c r="M12" t="n">
-        <v>17580</v>
+        <v>17420</v>
       </c>
       <c r="N12" t="n">
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>34577460345</v>
+        <v>37323251335</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1539,10 +1539,10 @@
         <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-95000</v>
+        <v>-177000</v>
       </c>
       <c r="S12" t="n">
-        <v>-29000</v>
+        <v>-36000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13230</v>
+        <v>13130</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.49%</t>
+          <t>'-1.94%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
         <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H13" t="n">
         <v>3.18</v>
@@ -1607,31 +1607,31 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13430</v>
+        <v>13390</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>13770</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>13830</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>13120</v>
       </c>
       <c r="N13" t="n">
         <v>3.12</v>
       </c>
       <c r="O13" t="n">
-        <v>22445000000</v>
+        <v>23556466910</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>20300</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3020</v>
       </c>
       <c r="R13" t="n">
-        <v>-255000</v>
+        <v>-292000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>236000</v>
+        <v>1737000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-2.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>142</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>97</v>
+        <v>445</v>
       </c>
       <c r="G14" t="n">
-        <v>735</v>
+        <v>1508</v>
       </c>
       <c r="H14" t="n">
-        <v>4.12</v>
+        <v>49.71</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>241000</v>
+        <v>1773000</v>
       </c>
       <c r="K14" t="n">
-        <v>253000</v>
+        <v>1728000</v>
       </c>
       <c r="L14" t="n">
-        <v>257000</v>
+        <v>1779000</v>
       </c>
       <c r="M14" t="n">
-        <v>235000</v>
+        <v>1725000</v>
       </c>
       <c r="N14" t="n">
-        <v>4.08</v>
+        <v>49.76</v>
       </c>
       <c r="O14" t="n">
-        <v>71103689000</v>
+        <v>2096791155000</v>
       </c>
       <c r="P14" t="n">
-        <v>1233000</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>120000</v>
+        <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>-43000</v>
+        <v>-199000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>-57000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 아일리아, 캐나다/독일 관련 모멘텀 언급. 외인 공매도 숏커버링에 따른 상승 기대.</t>
+          <t>외인 매도세와 국내 증시 전반의 부진 속 추세 하락 우려. 정치적 요인 및 공매도 이슈도 부정적 영향으로 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['경구용인슐린', 'L/O', '공매도']</t>
+          <t>['외인 매도', '추세 하락', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1736000</v>
+        <v>235000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-2.49%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>144</v>
       </c>
       <c r="F15" t="n">
-        <v>449</v>
+        <v>98</v>
       </c>
       <c r="G15" t="n">
-        <v>1612</v>
+        <v>751</v>
       </c>
       <c r="H15" t="n">
-        <v>49.71</v>
+        <v>4.12</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1773000</v>
+        <v>241000</v>
       </c>
       <c r="K15" t="n">
-        <v>1728000</v>
+        <v>253000</v>
       </c>
       <c r="L15" t="n">
-        <v>1779000</v>
+        <v>257000</v>
       </c>
       <c r="M15" t="n">
-        <v>1725000</v>
+        <v>234500</v>
       </c>
       <c r="N15" t="n">
-        <v>49.76</v>
+        <v>4.08</v>
       </c>
       <c r="O15" t="n">
-        <v>1997686656000</v>
+        <v>72947687000</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>1233000</v>
       </c>
       <c r="Q15" t="n">
-        <v>403000</v>
+        <v>120000</v>
       </c>
       <c r="R15" t="n">
-        <v>-147000</v>
+        <v>-49000</v>
       </c>
       <c r="S15" t="n">
-        <v>-47000</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>증시 전반의 하락세 속 SK하이닉스의 저평가 주장. 외국인 매도세 및 공매도에 대한 불만 표출.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다/독일 관련 계약 기대감. 외국인 숏커버링 및 거래량 동반 상승은 긍정적 요인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '외국인매도', '공매도']</t>
+          <t>['경구용 인슐린', 'L/O', '거래량']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18140</v>
+        <v>17940</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G16" t="n">
-        <v>779</v>
+        <v>802</v>
       </c>
       <c r="H16" t="n">
         <v>4.92</v>
@@ -1892,13 +1892,13 @@
         <v>19870</v>
       </c>
       <c r="M16" t="n">
-        <v>18120</v>
+        <v>17900</v>
       </c>
       <c r="N16" t="n">
         <v>3.81</v>
       </c>
       <c r="O16" t="n">
-        <v>241392517465</v>
+        <v>250652577400</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1907,10 +1907,10 @@
         <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-317000</v>
+        <v>-491000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46075</v>
+        <v>45800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.80%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F17" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G17" t="n">
-        <v>1784</v>
+        <v>1894</v>
       </c>
       <c r="H17" t="n">
         <v>14.12</v>
@@ -1990,7 +1990,7 @@
         <v>14.1</v>
       </c>
       <c r="O17" t="n">
-        <v>30052291975</v>
+        <v>31579364900</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -1999,23 +1999,23 @@
         <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="S17" t="n">
         <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 언급하며 빅호재 기대감 형성. 공매도 세력에 대한 비판과 함께 연말 목표가 30만원 이상 제시.</t>
+          <t>FDA 승인 가능성(90% 이상) 및 대규모 매출/영업이익 창출 전망, 공매도 세력과의 갈등 속 기대감 고조. 기타법인 자사주 매집도 긍정적.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['FDA승인', '공매도', '매출']</t>
+          <t>['FDA 승인', '매출 전망', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12520</v>
+        <v>12450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.77%</t>
+          <t>'-4.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="H18" t="n">
         <v>1.42</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>33781455735</v>
+        <v>34134482570</v>
       </c>
       <c r="P18" t="n">
         <v>22250</v>
@@ -2091,10 +2091,10 @@
         <v>6000</v>
       </c>
       <c r="R18" t="n">
-        <v>-100000</v>
+        <v>-101000</v>
       </c>
       <c r="S18" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2127,184 +2127,184 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30200</v>
+        <v>6640</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.01</v>
+        <v>-0.77</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H19" t="n">
-        <v>10.78</v>
+        <v>1.1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>31750</v>
+        <v>6980</v>
       </c>
       <c r="K19" t="n">
-        <v>32600</v>
+        <v>7000</v>
       </c>
       <c r="L19" t="n">
-        <v>32850</v>
+        <v>7240</v>
       </c>
       <c r="M19" t="n">
-        <v>30200</v>
+        <v>6580</v>
       </c>
       <c r="N19" t="n">
-        <v>10.77</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
-        <v>76032318825</v>
+        <v>42165197410</v>
       </c>
       <c r="P19" t="n">
-        <v>75900</v>
+        <v>11370</v>
       </c>
       <c r="Q19" t="n">
-        <v>15960</v>
+        <v>3300</v>
       </c>
       <c r="R19" t="n">
-        <v>-379000</v>
+        <v>180000</v>
       </c>
       <c r="S19" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 열위 및 주가 하락에 대한 불만 표출. 회사 관리 및 IR에 대한 비판.</t>
+          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가온전선', '주가관리', 'IR']</t>
+          <t>['망분리', '보안주', '실적']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6620</v>
+        <v>30100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.16%</t>
+          <t>'-5.20%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.77</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="G20" t="n">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1</v>
+        <v>10.78</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6980</v>
+        <v>31750</v>
       </c>
       <c r="K20" t="n">
-        <v>7000</v>
+        <v>32600</v>
       </c>
       <c r="L20" t="n">
-        <v>7240</v>
+        <v>32850</v>
       </c>
       <c r="M20" t="n">
-        <v>6580</v>
+        <v>30050</v>
       </c>
       <c r="N20" t="n">
-        <v>1.87</v>
+        <v>10.77</v>
       </c>
       <c r="O20" t="n">
-        <v>41618841250</v>
+        <v>79878062000</v>
       </c>
       <c r="P20" t="n">
-        <v>11370</v>
+        <v>75900</v>
       </c>
       <c r="Q20" t="n">
-        <v>3300</v>
+        <v>15960</v>
       </c>
       <c r="R20" t="n">
-        <v>-37000</v>
+        <v>-540000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
+          <t>가온전선과의 비교 열위 및 주가 하락에 대한 불만 표출. 회사 관리 및 IR에 대한 비판.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['망분리', '보안주', '실적']</t>
+          <t>['가온전선', '주가관리', 'IR']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>001440</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261007_11.xlsx
+++ b/data/trending_integrated_20261007_11.xlsx
@@ -581,10 +581,10 @@
         <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26193657844</v>
+        <v>26197095524</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16970</v>
+        <v>17080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.12%</t>
+          <t>'+14.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="H3" t="n">
         <v>2.37</v>
@@ -702,7 +702,7 @@
         <v>1.39</v>
       </c>
       <c r="O3" t="n">
-        <v>209633214760</v>
+        <v>217338887120</v>
       </c>
       <c r="P3" t="n">
         <v>17590</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 보안사고 증가 추세 속, 양자보안 기술 공급 논의 등 긍정적 뉴스에 기반한 주가 상승 전망. 주포의 물량 확보도 언급.</t>
+          <t>개인정보 유출 이슈와 함께 보안주 강세 전망. 농협, KDB생명 해킹 방어 및 양자보안 공급 논의 언급. 주포 보유 가능성 제기.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['개인정보 유출', '양자보안', '주포']</t>
+          <t>['보안주', '양자보안', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26000</v>
+        <v>14080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.29%</t>
+          <t>'+14.19%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>185</v>
+        <v>95</v>
       </c>
       <c r="H4" t="n">
-        <v>2.82</v>
+        <v>0.79</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>22950</v>
+        <v>12330</v>
       </c>
       <c r="K4" t="n">
-        <v>26200</v>
+        <v>12580</v>
       </c>
       <c r="L4" t="n">
-        <v>27600</v>
+        <v>14260</v>
       </c>
       <c r="M4" t="n">
-        <v>25550</v>
+        <v>12300</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>0.48</v>
       </c>
       <c r="O4" t="n">
-        <v>84608364850</v>
+        <v>149994474760</v>
       </c>
       <c r="P4" t="n">
-        <v>30100</v>
+        <v>20850</v>
       </c>
       <c r="Q4" t="n">
-        <v>11140</v>
+        <v>4020</v>
       </c>
       <c r="R4" t="n">
-        <v>223000</v>
+        <v>-65000</v>
       </c>
       <c r="S4" t="n">
-        <v>-202000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
+          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유리기판', '주포', 'IR']</t>
+          <t>['가스터빈', '원전', '납품']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7630</v>
+        <v>7650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.04%</t>
+          <t>'+13.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="H5" t="n">
         <v>5.12</v>
@@ -886,7 +886,7 @@
         <v>5.14</v>
       </c>
       <c r="O5" t="n">
-        <v>53089038200</v>
+        <v>53937898985</v>
       </c>
       <c r="P5" t="n">
         <v>23500</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13900</v>
+        <v>25850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.73%</t>
+          <t>'+12.64%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>194</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>12330</v>
+        <v>22950</v>
       </c>
       <c r="K6" t="n">
-        <v>12580</v>
+        <v>26200</v>
       </c>
       <c r="L6" t="n">
-        <v>14260</v>
+        <v>27600</v>
       </c>
       <c r="M6" t="n">
-        <v>12300</v>
+        <v>25550</v>
       </c>
       <c r="N6" t="n">
-        <v>0.48</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>145041686640</v>
+        <v>86245420525</v>
       </c>
       <c r="P6" t="n">
-        <v>20850</v>
+        <v>30100</v>
       </c>
       <c r="Q6" t="n">
-        <v>4020</v>
+        <v>11140</v>
       </c>
       <c r="R6" t="n">
-        <v>-65000</v>
+        <v>223000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-202000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
+          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전', '납품']</t>
+          <t>['유리기판', '주포', 'IR']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10700</v>
+        <v>10610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.65%</t>
+          <t>'+9.72%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F7" t="n">
         <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H7" t="n">
         <v>5.01</v>
@@ -1070,7 +1070,7 @@
         <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>15670069590</v>
+        <v>15934739460</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2595</v>
+        <v>2615</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.81%</t>
+          <t>'+9.64%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
         <v>0.82</v>
@@ -1162,7 +1162,7 @@
         <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>8378125429</v>
+        <v>8468876059</v>
       </c>
       <c r="P8" t="n">
         <v>4760</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5280</v>
+        <v>5250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.39%</t>
+          <t>'+4.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
         <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>177858302510</v>
+        <v>180603062410</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기타법인 대규모 자사주 매집 및 2200억 규모 수주 계약(공시 예정) 등 구체적 근거 기반 상승 기대감. 미 증시 호조 및 JP모건 순매수도 긍정적 요인.</t>
+          <t>기타법인의 자사주 매집 및 2200억 규모 수주 계약 공시 임박 기대감. 미국 증시 호조 영향 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G10" t="n">
-        <v>1549</v>
+        <v>1536</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2172546580250</v>
+        <v>2236225990000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 산업 부진 및 노조 이슈 속, 기관/외인 매도세 지속. 정치적 요인에 따른 시장 불안감도 언급.</t>
+          <t>반도체 노조 문제와 정치적 이슈 언급. 100조 영업이익 대비 주가 부진 비판. 기관, 법인 매도세 지적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '노조', '외인']</t>
+          <t>['반도체', '노조', '기관']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="F11" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G11" t="n">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>111250397300</v>
+        <v>112312868200</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>구글-컨스텔레이션 3.6GW 전력구매 계약 뉴스 기반 원전주 급등 기대. 웨스팅하우스 계약 체결 공시 가능성 언급.</t>
+          <t>미국 원전주 급등에 따른 국내 원전주 동반 상승 기대. 구글의 전력구매 계약 호재 언급. 공매도 세력 대응 및 연기금 동향 주시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전주', '전력구매계약', '공시']</t>
+          <t>['원전주', '전력구매', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17490</v>
+        <v>17480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.46%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>37323251335</v>
+        <v>38322673825</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1575,79 +1575,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13130</v>
+        <v>236500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.94%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="G13" t="n">
-        <v>73</v>
+        <v>762</v>
       </c>
       <c r="H13" t="n">
-        <v>3.18</v>
+        <v>4.12</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13390</v>
+        <v>241000</v>
       </c>
       <c r="K13" t="n">
-        <v>13770</v>
+        <v>253000</v>
       </c>
       <c r="L13" t="n">
-        <v>13830</v>
+        <v>257000</v>
       </c>
       <c r="M13" t="n">
-        <v>13120</v>
+        <v>233500</v>
       </c>
       <c r="N13" t="n">
-        <v>3.12</v>
+        <v>4.08</v>
       </c>
       <c r="O13" t="n">
-        <v>23556466910</v>
+        <v>74985509750</v>
       </c>
       <c r="P13" t="n">
-        <v>20300</v>
+        <v>1233000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3020</v>
+        <v>120000</v>
       </c>
       <c r="R13" t="n">
-        <v>-292000</v>
+        <v>-49000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다/독일 관련 계약 기대감. 외국인 숏커버링 및 거래량 동반 상승은 긍정적 요인.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['경구용 인슐린', 'L/O', '거래량']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1737000</v>
+        <v>1736000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.03%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="G14" t="n">
-        <v>1508</v>
+        <v>1532</v>
       </c>
       <c r="H14" t="n">
         <v>49.71</v>
@@ -1714,7 +1714,7 @@
         <v>49.76</v>
       </c>
       <c r="O14" t="n">
-        <v>2096791155000</v>
+        <v>2151689599500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1759,79 +1759,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235000</v>
+        <v>13110</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.49%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>751</v>
+        <v>75</v>
       </c>
       <c r="H15" t="n">
-        <v>4.12</v>
+        <v>3.18</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>241000</v>
+        <v>13390</v>
       </c>
       <c r="K15" t="n">
-        <v>253000</v>
+        <v>13770</v>
       </c>
       <c r="L15" t="n">
-        <v>257000</v>
+        <v>13830</v>
       </c>
       <c r="M15" t="n">
-        <v>234500</v>
+        <v>13080</v>
       </c>
       <c r="N15" t="n">
-        <v>4.08</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>72947687000</v>
+        <v>23890451825</v>
       </c>
       <c r="P15" t="n">
-        <v>1233000</v>
+        <v>20300</v>
       </c>
       <c r="Q15" t="n">
-        <v>120000</v>
+        <v>3020</v>
       </c>
       <c r="R15" t="n">
-        <v>-49000</v>
+        <v>-292000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다/독일 관련 계약 기대감. 외국인 숏커버링 및 거래량 동반 상승은 긍정적 요인.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', 'L/O', '거래량']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17940</v>
+        <v>17950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F16" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G16" t="n">
-        <v>802</v>
+        <v>824</v>
       </c>
       <c r="H16" t="n">
         <v>4.92</v>
@@ -1892,13 +1892,13 @@
         <v>19870</v>
       </c>
       <c r="M16" t="n">
-        <v>17900</v>
+        <v>17880</v>
       </c>
       <c r="N16" t="n">
         <v>3.81</v>
       </c>
       <c r="O16" t="n">
-        <v>250652577400</v>
+        <v>254146352120</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨황의 광통신 지지 언급에 따른 기대감. 외인 매도세 관찰.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급. 19870원 목표가 제시. 외인 대량 매도 발생.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '젠슨황', '외인수급']</t>
+          <t>['광통신', '모멘텀', '외인 매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F17" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G17" t="n">
-        <v>1894</v>
+        <v>1943</v>
       </c>
       <c r="H17" t="n">
         <v>14.12</v>
@@ -1990,7 +1990,7 @@
         <v>14.1</v>
       </c>
       <c r="O17" t="n">
-        <v>31579364900</v>
+        <v>32343908925</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성(90% 이상) 및 대규모 매출/영업이익 창출 전망, 공매도 세력과의 갈등 속 기대감 고조. 기타법인 자사주 매집도 긍정적.</t>
+          <t>FDA 승인 가능성 90% 이상 및 시기 문제 언급. 연말 30만원 이상 목표가 제시. 공매도 세력 비판 및 기대감 고조.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['FDA 승인', '매출 전망', '공매도']</t>
+          <t>['FDA 승인', '공매도', '기대감']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12450</v>
+        <v>6710</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.30%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.88</v>
+        <v>-0.77</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="H18" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13010</v>
+        <v>6980</v>
       </c>
       <c r="K18" t="n">
-        <v>12330</v>
+        <v>7000</v>
       </c>
       <c r="L18" t="n">
-        <v>13560</v>
+        <v>7240</v>
       </c>
       <c r="M18" t="n">
-        <v>12260</v>
+        <v>6580</v>
       </c>
       <c r="N18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O18" t="n">
+        <v>42684699050</v>
+      </c>
+      <c r="P18" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R18" t="n">
+        <v>180000</v>
+      </c>
+      <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="n">
-        <v>34134482570</v>
-      </c>
-      <c r="P18" t="n">
-        <v>22250</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6000</v>
-      </c>
-      <c r="R18" t="n">
-        <v>-101000</v>
-      </c>
-      <c r="S18" t="n">
-        <v>9000</v>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['망분리', '보안주', '실적']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6640</v>
+        <v>12480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-4.07%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.77</v>
+        <v>1.88</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6980</v>
+        <v>13010</v>
       </c>
       <c r="K19" t="n">
-        <v>7000</v>
+        <v>12330</v>
       </c>
       <c r="L19" t="n">
-        <v>7240</v>
+        <v>13560</v>
       </c>
       <c r="M19" t="n">
-        <v>6580</v>
+        <v>12260</v>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>42165197410</v>
+        <v>34419343750</v>
       </c>
       <c r="P19" t="n">
-        <v>11370</v>
+        <v>22250</v>
       </c>
       <c r="Q19" t="n">
-        <v>3300</v>
+        <v>6000</v>
       </c>
       <c r="R19" t="n">
-        <v>180000</v>
+        <v>-101000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['망분리', '보안주', '실적']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30100</v>
+        <v>30200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.20%</t>
+          <t>'-4.88%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H20" t="n">
         <v>10.78</v>
@@ -2266,7 +2266,7 @@
         <v>10.77</v>
       </c>
       <c r="O20" t="n">
-        <v>79878062000</v>
+        <v>80876471775</v>
       </c>
       <c r="P20" t="n">
         <v>75900</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 열위 및 주가 하락에 대한 불만 표출. 회사 관리 및 IR에 대한 비판.</t>
+          <t>가온전선과 비교하며 주가 부진 언급. 외인 매도세와 주가 하락 속도 지적. 회사 관리 부실 가능성 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['가온전선', '주가관리', 'IR']</t>
+          <t>['주가 부진', '외인 매도', '회사 관리']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20261007_11.xlsx
+++ b/data/trending_integrated_20261007_11.xlsx
@@ -578,10 +578,10 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26197095524</v>
+        <v>26208201534</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17080</v>
+        <v>7760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.86%</t>
+          <t>'+14.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.98</v>
+        <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="H3" t="n">
-        <v>2.37</v>
+        <v>5.12</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14870</v>
+        <v>6750</v>
       </c>
       <c r="K3" t="n">
-        <v>15480</v>
+        <v>6710</v>
       </c>
       <c r="L3" t="n">
-        <v>17590</v>
+        <v>8310</v>
       </c>
       <c r="M3" t="n">
-        <v>14600</v>
+        <v>6690</v>
       </c>
       <c r="N3" t="n">
-        <v>1.39</v>
+        <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>217338887120</v>
+        <v>55877361500</v>
       </c>
       <c r="P3" t="n">
-        <v>17590</v>
+        <v>23500</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>2890</v>
       </c>
       <c r="R3" t="n">
-        <v>-83000</v>
+        <v>-688000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>개인정보 유출 이슈와 함께 보안주 강세 전망. 농협, KDB생명 해킹 방어 및 양자보안 공급 논의 언급. 주포 보유 가능성 제기.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 관련 뉴스 언급. 성수 메가프로젝트 및 건설 기초 소재 대장주로서의 위치 강조. 10만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', '주포']</t>
+          <t>['용적률', '그린벨트', '건설']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14080</v>
+        <v>16820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.19%</t>
+          <t>'+13.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.31</v>
+        <v>0.98</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="H4" t="n">
-        <v>0.79</v>
+        <v>2.37</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12330</v>
+        <v>14870</v>
       </c>
       <c r="K4" t="n">
-        <v>12580</v>
+        <v>15480</v>
       </c>
       <c r="L4" t="n">
-        <v>14260</v>
+        <v>17590</v>
       </c>
       <c r="M4" t="n">
-        <v>12300</v>
+        <v>14600</v>
       </c>
       <c r="N4" t="n">
-        <v>0.48</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>149994474760</v>
+        <v>220620542550</v>
       </c>
       <c r="P4" t="n">
-        <v>20850</v>
+        <v>17590</v>
       </c>
       <c r="Q4" t="n">
-        <v>4020</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-65000</v>
+        <v>-83000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
+          <t>개인정보 유출 사고 발생 및 보안주 강세에 따른 주가 상승 기대감. 양자보안 기술 부각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전', '납품']</t>
+          <t>['개인정보 유출', '보안주', '양자보안']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7650</v>
+        <v>25900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.33%</t>
+          <t>'+12.85%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="H5" t="n">
-        <v>5.12</v>
+        <v>2.82</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6750</v>
+        <v>22950</v>
       </c>
       <c r="K5" t="n">
-        <v>6710</v>
+        <v>26200</v>
       </c>
       <c r="L5" t="n">
-        <v>8310</v>
+        <v>27600</v>
       </c>
       <c r="M5" t="n">
-        <v>6690</v>
+        <v>25550</v>
       </c>
       <c r="N5" t="n">
-        <v>5.14</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>53937898985</v>
+        <v>88308888525</v>
       </c>
       <c r="P5" t="n">
-        <v>23500</v>
+        <v>30100</v>
       </c>
       <c r="Q5" t="n">
-        <v>2890</v>
+        <v>11140</v>
       </c>
       <c r="R5" t="n">
-        <v>-688000</v>
+        <v>223000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-202000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 관련 뉴스 언급. 성수 메가프로젝트 및 건설 기초 소재 대장주로서의 위치 강조. 10만원 목표가 제시.</t>
+          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '건설']</t>
+          <t>['유리기판', '주포', 'IR']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25850</v>
+        <v>13810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.64%</t>
+          <t>'+12.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>22950</v>
+        <v>12330</v>
       </c>
       <c r="K6" t="n">
-        <v>26200</v>
+        <v>12580</v>
       </c>
       <c r="L6" t="n">
-        <v>27600</v>
+        <v>14260</v>
       </c>
       <c r="M6" t="n">
-        <v>25550</v>
+        <v>12300</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>0.48</v>
       </c>
       <c r="O6" t="n">
-        <v>86245420525</v>
+        <v>153802281005</v>
       </c>
       <c r="P6" t="n">
-        <v>30100</v>
+        <v>20850</v>
       </c>
       <c r="Q6" t="n">
-        <v>11140</v>
+        <v>4020</v>
       </c>
       <c r="R6" t="n">
-        <v>223000</v>
+        <v>-65000</v>
       </c>
       <c r="S6" t="n">
-        <v>-202000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
+          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리기판', '주포', 'IR']</t>
+          <t>['가스터빈', '원전', '납품']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1038,13 @@
         <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
         <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H7" t="n">
         <v>5.01</v>
@@ -1070,7 +1070,7 @@
         <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>15934739460</v>
+        <v>16134867340</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>전염병 테마주로서의 기대감과 함께, 러시아/케냐 발 질병 확산 소식에 따른 변동성 예상. 일부 부정적 분석도 혼재.</t>
+          <t>신종 전염병 관련 테마주로 부각되며 주가 상승 기대감 형성. 일부 부정적 시각과 함께 투기적 움직임.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전염병', '테마주', '변동성']</t>
+          <t>['전염병', '테마주', '급등']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2615</v>
+        <v>2585</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.64%</t>
+          <t>'+8.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.29</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H8" t="n">
         <v>0.82</v>
@@ -1162,7 +1162,7 @@
         <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>8468876059</v>
+        <v>8537850944</v>
       </c>
       <c r="P8" t="n">
         <v>4760</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5250</v>
+        <v>5200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.79%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>180603062410</v>
+        <v>184591896460</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기타법인의 자사주 매집 및 2200억 규모 수주 계약 공시 임박 기대감. 미국 증시 호조 영향 언급.</t>
+          <t>대규모 수주 계약 임박 및 미국 증시 강세에 따른 주가 급등 전망. 기타법인의 자사주 매집 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주 매집', '수주 계약', '기대감']</t>
+          <t>['수주', '자사주', '급등']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G10" t="n">
-        <v>1536</v>
+        <v>1547</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2236225990000</v>
+        <v>2290614427250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 노조 문제와 정치적 이슈 언급. 100조 영업이익 대비 주가 부진 비판. 기관, 법인 매도세 지적.</t>
+          <t>반도체 업황 부진 및 노조 이슈 언급. 정치적 발언과 함께 주가 상승에 대한 회의적인 시각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '노조', '기관']</t>
+          <t>['반도체', '노조', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80750</v>
+        <v>81000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-0.61%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G11" t="n">
-        <v>671</v>
+        <v>693</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>112312868200</v>
+        <v>115422195600</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17480</v>
+        <v>17530</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-1.24%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>38322673825</v>
+        <v>39406505390</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1575,79 +1575,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>236500</v>
+        <v>13150</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-1.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>762</v>
+        <v>76</v>
       </c>
       <c r="H13" t="n">
-        <v>4.12</v>
+        <v>3.18</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>241000</v>
+        <v>13390</v>
       </c>
       <c r="K13" t="n">
-        <v>253000</v>
+        <v>13770</v>
       </c>
       <c r="L13" t="n">
-        <v>257000</v>
+        <v>13830</v>
       </c>
       <c r="M13" t="n">
-        <v>233500</v>
+        <v>13080</v>
       </c>
       <c r="N13" t="n">
-        <v>4.08</v>
+        <v>3.12</v>
       </c>
       <c r="O13" t="n">
-        <v>74985509750</v>
+        <v>24106805320</v>
       </c>
       <c r="P13" t="n">
-        <v>1233000</v>
+        <v>20300</v>
       </c>
       <c r="Q13" t="n">
-        <v>120000</v>
+        <v>3020</v>
       </c>
       <c r="R13" t="n">
-        <v>-49000</v>
+        <v>-292000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다/독일 관련 계약 기대감. 외국인 숏커버링 및 거래량 동반 상승은 긍정적 요인.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', 'L/O', '거래량']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1736000</v>
+        <v>1741000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G14" t="n">
-        <v>1532</v>
+        <v>1575</v>
       </c>
       <c r="H14" t="n">
         <v>49.71</v>
@@ -1714,7 +1714,7 @@
         <v>49.76</v>
       </c>
       <c r="O14" t="n">
-        <v>2151689599500</v>
+        <v>2223183380000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외인 매도세와 국내 증시 전반의 부진 속 추세 하락 우려. 정치적 요인 및 공매도 이슈도 부정적 영향으로 언급.</t>
+          <t>반도체 업황 부진 및 외국인 매도세 지속에 따른 주가 하락 우려. 정치적 이슈와 공매도 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인 매도', '추세 하락', '공매도']</t>
+          <t>['반도체', '외국인', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,123 +1759,123 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13110</v>
+        <v>18140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>1.11</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="G15" t="n">
-        <v>75</v>
+        <v>837</v>
       </c>
       <c r="H15" t="n">
-        <v>3.18</v>
+        <v>4.92</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13390</v>
+        <v>18530</v>
       </c>
       <c r="K15" t="n">
-        <v>13770</v>
+        <v>18950</v>
       </c>
       <c r="L15" t="n">
-        <v>13830</v>
+        <v>19870</v>
       </c>
       <c r="M15" t="n">
-        <v>13080</v>
+        <v>17880</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>3.81</v>
       </c>
       <c r="O15" t="n">
-        <v>23890451825</v>
+        <v>257010287275</v>
       </c>
       <c r="P15" t="n">
-        <v>20300</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3020</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-292000</v>
+        <v>-491000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급. 19870원 목표가 제시. 외인 대량 매도 발생.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['광통신', '모멘텀', '외인 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17950</v>
+        <v>235500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.11</v>
+        <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G16" t="n">
-        <v>824</v>
+        <v>780</v>
       </c>
       <c r="H16" t="n">
-        <v>4.92</v>
+        <v>4.12</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18530</v>
+        <v>241000</v>
       </c>
       <c r="K16" t="n">
-        <v>18950</v>
+        <v>253000</v>
       </c>
       <c r="L16" t="n">
-        <v>19870</v>
+        <v>257000</v>
       </c>
       <c r="M16" t="n">
-        <v>17880</v>
+        <v>233500</v>
       </c>
       <c r="N16" t="n">
-        <v>3.81</v>
+        <v>4.08</v>
       </c>
       <c r="O16" t="n">
-        <v>254146352120</v>
+        <v>75911621750</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>1233000</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>120000</v>
       </c>
       <c r="R16" t="n">
-        <v>-491000</v>
+        <v>-49000</v>
       </c>
       <c r="S16" t="n">
         <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급. 19870원 목표가 제시. 외인 대량 매도 발생.</t>
+          <t>경구용 인슐린 등 신약 파이프라인에 대한 높은 기대감. 공매도 세력과의 갈등 및 거래량 증가 주목.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '모멘텀', '외인 매도']</t>
+          <t>['신약', '공매도', '거래량']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45800</v>
+        <v>46075</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.38%</t>
+          <t>'-2.80%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F17" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G17" t="n">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="H17" t="n">
         <v>14.12</v>
@@ -1990,7 +1990,7 @@
         <v>14.1</v>
       </c>
       <c r="O17" t="n">
-        <v>32343908925</v>
+        <v>32884581725</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6710</v>
+        <v>6760</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.77</v>
       </c>
       <c r="E18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H18" t="n">
         <v>1.1</v>
@@ -2082,7 +2082,7 @@
         <v>1.87</v>
       </c>
       <c r="O18" t="n">
-        <v>42684699050</v>
+        <v>43322915840</v>
       </c>
       <c r="P18" t="n">
         <v>11370</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12480</v>
+        <v>12540</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.07%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H19" t="n">
         <v>1.42</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>34419343750</v>
+        <v>34621509210</v>
       </c>
       <c r="P19" t="n">
         <v>22250</v>
@@ -2234,13 +2234,13 @@
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F20" t="n">
         <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="H20" t="n">
         <v>10.78</v>
@@ -2266,7 +2266,7 @@
         <v>10.77</v>
       </c>
       <c r="O20" t="n">
-        <v>80876471775</v>
+        <v>82668971775</v>
       </c>
       <c r="P20" t="n">
         <v>75900</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>가온전선과 비교하며 주가 부진 언급. 외인 매도세와 주가 하락 속도 지적. 회사 관리 부실 가능성 제기.</t>
+          <t>경쟁사 대비 저조한 주가 흐름 및 급락세에 대한 불만 표출. 단기 반등 기대감과 함께 부정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 부진', '외인 매도', '회사 관리']</t>
+          <t>['주가', '급락', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20261007_11.xlsx
+++ b/data/trending_integrated_20261007_11.xlsx
@@ -578,10 +578,10 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26208201534</v>
+        <v>26257250494</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7760</v>
+        <v>7900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.96%</t>
+          <t>'+17.04%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>55877361500</v>
+        <v>59200503440</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16820</v>
+        <v>16870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.11%</t>
+          <t>'+13.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.98</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H4" t="n">
         <v>2.37</v>
@@ -794,7 +794,7 @@
         <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>220620542550</v>
+        <v>223705943190</v>
       </c>
       <c r="P4" t="n">
         <v>17590</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>개인정보 유출 사고 발생 및 보안주 강세에 따른 주가 상승 기대감. 양자보안 기술 부각.</t>
+          <t>개인정보 유출 및 미국 보안주 상승에 따른 라온시큐어의 양자보안 기술 공급 기대감 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['개인정보 유출', '보안주', '양자보안']</t>
+          <t>['보안', '양자보안', '주가상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25900</v>
+        <v>25950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.85%</t>
+          <t>'+13.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
         <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H5" t="n">
         <v>2.82</v>
@@ -886,7 +886,7 @@
         <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>88308888525</v>
+        <v>89193883900</v>
       </c>
       <c r="P5" t="n">
         <v>30100</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13810</v>
+        <v>2640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.00%</t>
+          <t>'+10.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>12330</v>
+        <v>2385</v>
       </c>
       <c r="K6" t="n">
-        <v>12580</v>
+        <v>2510</v>
       </c>
       <c r="L6" t="n">
-        <v>14260</v>
+        <v>2900</v>
       </c>
       <c r="M6" t="n">
-        <v>12300</v>
+        <v>2505</v>
       </c>
       <c r="N6" t="n">
-        <v>0.48</v>
+        <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>153802281005</v>
+        <v>8901040481</v>
       </c>
       <c r="P6" t="n">
-        <v>20850</v>
+        <v>4760</v>
       </c>
       <c r="Q6" t="n">
-        <v>4020</v>
+        <v>973</v>
       </c>
       <c r="R6" t="n">
-        <v>-65000</v>
+        <v>-31000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전', '납품']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10610</v>
+        <v>10620</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.72%</t>
+          <t>'+9.82%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H7" t="n">
         <v>5.01</v>
@@ -1070,7 +1070,7 @@
         <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>16134867340</v>
+        <v>16384536740</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2585</v>
+        <v>13540</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.39%</t>
+          <t>'+9.81%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.29</v>
+        <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="H8" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2385</v>
+        <v>12330</v>
       </c>
       <c r="K8" t="n">
-        <v>2510</v>
+        <v>12580</v>
       </c>
       <c r="L8" t="n">
-        <v>2900</v>
+        <v>14260</v>
       </c>
       <c r="M8" t="n">
-        <v>2505</v>
+        <v>12300</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>8537850944</v>
+        <v>160594208880</v>
       </c>
       <c r="P8" t="n">
-        <v>4760</v>
+        <v>20850</v>
       </c>
       <c r="Q8" t="n">
-        <v>973</v>
+        <v>4020</v>
       </c>
       <c r="R8" t="n">
-        <v>-31000</v>
+        <v>-65000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['가스터빈', '원전', '납품']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>184591896460</v>
+        <v>187948298910</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대규모 수주 계약 임박 및 미국 증시 강세에 따른 주가 급등 전망. 기타법인의 자사주 매집 확인.</t>
+          <t>미국 증시 호조 및 2200억 규모 수주 계약 공시 기대감으로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '자사주', '급등']</t>
+          <t>['수주', '급등', '미국증시']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>271500</v>
+        <v>272500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.18%</t>
+          <t>'+0.18%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G10" t="n">
-        <v>1547</v>
+        <v>1499</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2290614427250</v>
+        <v>2345793777500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 및 노조 이슈 언급. 정치적 발언과 함께 주가 상승에 대한 회의적인 시각.</t>
+          <t>이재명 관련 정치적 언급과 함께 삼성전자 주가 부진에 대한 부정적 전망이 혼재된 게시글.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '노조', '주가']</t>
+          <t>['정치', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81000</v>
+        <v>81200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G11" t="n">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>115422195600</v>
+        <v>121040850850</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 원전주 급등에 따른 국내 원전주 동반 상승 기대. 구글의 전력구매 계약 호재 언급. 공매도 세력 대응 및 연기금 동향 주시.</t>
+          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 발표에 따른 두산에너빌리티 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전주', '전력구매', '공매도']</t>
+          <t>['원전', '전력구매', '계약']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17530</v>
+        <v>17590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.24%</t>
+          <t>'-0.90%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="H12" t="n">
         <v>9.5</v>
@@ -1530,7 +1530,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>39406505390</v>
+        <v>40376326950</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13150</v>
+        <v>13180</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-1.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13" t="n">
         <v>3.18</v>
@@ -1622,7 +1622,7 @@
         <v>3.12</v>
       </c>
       <c r="O13" t="n">
-        <v>24106805320</v>
+        <v>24197139960</v>
       </c>
       <c r="P13" t="n">
         <v>20300</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1741000</v>
+        <v>1742000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G14" t="n">
-        <v>1575</v>
+        <v>1595</v>
       </c>
       <c r="H14" t="n">
         <v>49.71</v>
@@ -1714,7 +1714,7 @@
         <v>49.76</v>
       </c>
       <c r="O14" t="n">
-        <v>2223183380000</v>
+        <v>2281203775500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 및 외국인 매도세 지속에 따른 주가 하락 우려. 정치적 이슈와 공매도 비판.</t>
+          <t>나스닥 하락, 외인 매도, 정치적 이슈 등으로 인한 SK하이닉스 주가 부진에 대한 불만과 공매도 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '주가']</t>
+          <t>['반도체', '외인', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18140</v>
+        <v>236750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-1.76%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.11</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G15" t="n">
-        <v>837</v>
+        <v>793</v>
       </c>
       <c r="H15" t="n">
-        <v>4.92</v>
+        <v>4.12</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18530</v>
+        <v>241000</v>
       </c>
       <c r="K15" t="n">
-        <v>18950</v>
+        <v>253000</v>
       </c>
       <c r="L15" t="n">
-        <v>19870</v>
+        <v>257000</v>
       </c>
       <c r="M15" t="n">
-        <v>17880</v>
+        <v>233500</v>
       </c>
       <c r="N15" t="n">
-        <v>3.81</v>
+        <v>4.08</v>
       </c>
       <c r="O15" t="n">
-        <v>257010287275</v>
+        <v>77440067250</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>1233000</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>120000</v>
       </c>
       <c r="R15" t="n">
-        <v>-491000</v>
+        <v>-49000</v>
       </c>
       <c r="S15" t="n">
         <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급. 19870원 목표가 제시. 외인 대량 매도 발생.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다, 독일 임상 결과 발표 기대감으로 인한 삼천당제약 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '모멘텀', '외인 매도']</t>
+          <t>['인슐린', 'L/O', '임상']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>235500</v>
+        <v>18100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.28%</t>
+          <t>'-2.32%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G16" t="n">
-        <v>780</v>
+        <v>868</v>
       </c>
       <c r="H16" t="n">
-        <v>4.12</v>
+        <v>4.92</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>241000</v>
+        <v>18530</v>
       </c>
       <c r="K16" t="n">
-        <v>253000</v>
+        <v>18950</v>
       </c>
       <c r="L16" t="n">
-        <v>257000</v>
+        <v>19870</v>
       </c>
       <c r="M16" t="n">
-        <v>233500</v>
+        <v>17880</v>
       </c>
       <c r="N16" t="n">
-        <v>4.08</v>
+        <v>3.81</v>
       </c>
       <c r="O16" t="n">
-        <v>75911621750</v>
+        <v>259117907210</v>
       </c>
       <c r="P16" t="n">
-        <v>1233000</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>120000</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-49000</v>
+        <v>-491000</v>
       </c>
       <c r="S16" t="n">
         <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>경구용 인슐린 등 신약 파이프라인에 대한 높은 기대감. 공매도 세력과의 갈등 및 거래량 증가 주목.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급에 따른 기대감과 외국인 매도에 대한 우려가 공존.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['신약', '공매도', '거래량']</t>
+          <t>['광통신', '미국증시', '외국인']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46075</v>
+        <v>6780</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.80%</t>
+          <t>'-2.87%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>-0.77</v>
       </c>
       <c r="E17" t="n">
-        <v>271</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>165</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>1973</v>
+        <v>191</v>
       </c>
       <c r="H17" t="n">
-        <v>14.12</v>
+        <v>1.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>47400</v>
+        <v>6980</v>
       </c>
       <c r="K17" t="n">
-        <v>46350</v>
+        <v>7000</v>
       </c>
       <c r="L17" t="n">
-        <v>47850</v>
+        <v>7240</v>
       </c>
       <c r="M17" t="n">
-        <v>45650</v>
+        <v>6580</v>
       </c>
       <c r="N17" t="n">
-        <v>14.1</v>
+        <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>32884581725</v>
+        <v>44228079485</v>
       </c>
       <c r="P17" t="n">
-        <v>69200</v>
+        <v>11370</v>
       </c>
       <c r="Q17" t="n">
-        <v>24150</v>
+        <v>3300</v>
       </c>
       <c r="R17" t="n">
-        <v>3000</v>
+        <v>180000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 및 시기 문제 언급. 연말 30만원 이상 목표가 제시. 공매도 세력 비판 및 기대감 고조.</t>
+          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '기대감']</t>
+          <t>['망분리', '보안주', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,43 +2023,43 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6760</v>
+        <v>46000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.15%</t>
+          <t>'-2.95%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.77</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>276</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="G18" t="n">
-        <v>188</v>
+        <v>1966</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1</v>
+        <v>14.12</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6980</v>
+        <v>47400</v>
       </c>
       <c r="K18" t="n">
-        <v>7000</v>
+        <v>46350</v>
       </c>
       <c r="L18" t="n">
-        <v>7240</v>
+        <v>47850</v>
       </c>
       <c r="M18" t="n">
-        <v>6580</v>
+        <v>45650</v>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>14.1</v>
       </c>
       <c r="O18" t="n">
-        <v>43322915840</v>
+        <v>33281932050</v>
       </c>
       <c r="P18" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R18" t="n">
-        <v>180000</v>
+        <v>3000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>망분리 완화 관련 금융권 공략 소식 및 3분기 역대급 실적 기대감 언급. 라온시큐어와의 비교 및 보안주로서의 성장 가능성 제시. 시가총액 1조 달성.</t>
+          <t>FDA 승인 가능성 90% 이상 및 2~3조원 매출 기대감으로 인한 HLB 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['망분리', '보안주', '실적']</t>
+          <t>['FDA', '매출', '신약']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12540</v>
+        <v>12450</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-4.30%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="H19" t="n">
         <v>1.42</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>34621509210</v>
+        <v>34784753550</v>
       </c>
       <c r="P19" t="n">
         <v>22250</v>
@@ -2223,18 +2223,18 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30200</v>
+        <v>30150</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-5.04%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" t="n">
         <v>60</v>
@@ -2266,7 +2266,7 @@
         <v>10.77</v>
       </c>
       <c r="O20" t="n">
-        <v>82668971775</v>
+        <v>83886011375</v>
       </c>
       <c r="P20" t="n">
         <v>75900</v>

--- a/data/trending_integrated_20261007_11.xlsx
+++ b/data/trending_integrated_20261007_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26257250494</v>
+        <v>26267231284</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7900</v>
+        <v>7750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.04%</t>
+          <t>'+14.81%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>59200503440</v>
+        <v>62016547715</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16870</v>
+        <v>26275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.45%</t>
+          <t>'+14.49%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H4" t="n">
-        <v>2.37</v>
+        <v>2.82</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14870</v>
+        <v>22950</v>
       </c>
       <c r="K4" t="n">
-        <v>15480</v>
+        <v>26200</v>
       </c>
       <c r="L4" t="n">
-        <v>17590</v>
+        <v>27600</v>
       </c>
       <c r="M4" t="n">
-        <v>14600</v>
+        <v>25550</v>
       </c>
       <c r="N4" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>223705943190</v>
+        <v>90050222050</v>
       </c>
       <c r="P4" t="n">
-        <v>17590</v>
+        <v>30100</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>11140</v>
       </c>
       <c r="R4" t="n">
-        <v>-83000</v>
+        <v>223000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-202000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 미국 보안주 상승에 따른 라온시큐어의 양자보안 기술 공급 기대감 및 주가 상승 전망.</t>
+          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안', '양자보안', '주가상승']</t>
+          <t>['유리기판', '주포', 'IR']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25950</v>
+        <v>16930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.07%</t>
+          <t>'+13.85%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H5" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K5" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L5" t="n">
-        <v>27600</v>
+        <v>17590</v>
       </c>
       <c r="M5" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>89193883900</v>
+        <v>227319511460</v>
       </c>
       <c r="P5" t="n">
-        <v>30100</v>
+        <v>17590</v>
       </c>
       <c r="Q5" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>223000</v>
+        <v>-83000</v>
       </c>
       <c r="S5" t="n">
-        <v>-202000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
+          <t>연이은 개인정보 유출 사건으로 보안주 대세론 부각. 양자보안 기술을 바탕으로 10곳 이상 공급 논의 중.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유리기판', '주포', 'IR']</t>
+          <t>['보안', '양자보안', '개인정보']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2640</v>
+        <v>13500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.69%</t>
+          <t>'+9.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.29</v>
+        <v>0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="H6" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2385</v>
+        <v>12330</v>
       </c>
       <c r="K6" t="n">
-        <v>2510</v>
+        <v>12580</v>
       </c>
       <c r="L6" t="n">
-        <v>2900</v>
+        <v>14260</v>
       </c>
       <c r="M6" t="n">
-        <v>2505</v>
+        <v>12300</v>
       </c>
       <c r="N6" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="O6" t="n">
-        <v>8901040481</v>
+        <v>164004319710</v>
       </c>
       <c r="P6" t="n">
-        <v>4760</v>
+        <v>20850</v>
       </c>
       <c r="Q6" t="n">
-        <v>973</v>
+        <v>4020</v>
       </c>
       <c r="R6" t="n">
-        <v>-31000</v>
+        <v>-65000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['가스터빈', '원전', '납품']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10620</v>
+        <v>2610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.82%</t>
+          <t>'+9.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>295</v>
+        <v>59</v>
       </c>
       <c r="H7" t="n">
-        <v>5.01</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9670</v>
+        <v>2385</v>
       </c>
       <c r="K7" t="n">
-        <v>11020</v>
+        <v>2510</v>
       </c>
       <c r="L7" t="n">
-        <v>11030</v>
+        <v>2900</v>
       </c>
       <c r="M7" t="n">
-        <v>10300</v>
+        <v>2505</v>
       </c>
       <c r="N7" t="n">
-        <v>4.84</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>16384536740</v>
+        <v>8952643736</v>
       </c>
       <c r="P7" t="n">
-        <v>15900</v>
+        <v>4760</v>
       </c>
       <c r="Q7" t="n">
-        <v>6310</v>
+        <v>973</v>
       </c>
       <c r="R7" t="n">
-        <v>-216000</v>
+        <v>-31000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신종 전염병 관련 테마주로 부각되며 주가 상승 기대감 형성. 일부 부정적 시각과 함께 투기적 움직임.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전염병', '테마주', '급등']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,91 +1103,91 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13540</v>
+        <v>10550</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.81%</t>
+          <t>'+9.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>111</v>
+        <v>306</v>
       </c>
       <c r="H8" t="n">
-        <v>0.79</v>
+        <v>5.01</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12330</v>
+        <v>9670</v>
       </c>
       <c r="K8" t="n">
-        <v>12580</v>
+        <v>11020</v>
       </c>
       <c r="L8" t="n">
-        <v>14260</v>
+        <v>11030</v>
       </c>
       <c r="M8" t="n">
-        <v>12300</v>
+        <v>10300</v>
       </c>
       <c r="N8" t="n">
-        <v>0.48</v>
+        <v>4.84</v>
       </c>
       <c r="O8" t="n">
-        <v>160594208880</v>
+        <v>16648291520</v>
       </c>
       <c r="P8" t="n">
-        <v>20850</v>
+        <v>15900</v>
       </c>
       <c r="Q8" t="n">
-        <v>4020</v>
+        <v>6310</v>
       </c>
       <c r="R8" t="n">
-        <v>-65000</v>
+        <v>-216000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>한화파워 가스터빈 블레이드 납품 개시 및 원전, 데이터센터 관련 사업 언급. 14,200원 돌파 시 급등 예상 및 텐버거 기대감 표시. 거래량 증가 및 손바뀜 확인.</t>
+          <t>페스트, 에볼라 등 다양한 질병 테마주로 언급되며 상한가 기대감 형성. 모건의 매수세 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전', '납품']</t>
+          <t>['테마주', '페스트', '에볼라']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.79%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3.32</v>
       </c>
       <c r="E9" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="H9" t="n">
         <v>4.72</v>
@@ -1254,7 +1254,7 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>187948298910</v>
+        <v>193602240400</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 호조 및 2200억 규모 수주 계약 공시 기대감으로 인한 급등 전망.</t>
+          <t>2200억 규모 수주 계약 공시 임박 루머와 함께 급등 기대감 형성. 미국 증시 호조 영향.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '급등', '미국증시']</t>
+          <t>['수주', '공시', '급등']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272500</v>
+        <v>272750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.18%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G10" t="n">
-        <v>1499</v>
+        <v>1472</v>
       </c>
       <c r="H10" t="n">
         <v>46.37</v>
@@ -1346,7 +1346,7 @@
         <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2345793777500</v>
+        <v>2385381710000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이재명 관련 정치적 언급과 함께 삼성전자 주가 부진에 대한 부정적 전망이 혼재된 게시글.</t>
+          <t>정치적 이슈와 연관된 부정적 여론 속에서 소폭 상승했으나, 4개월간 30만원 돌파 실패. 매수 주체에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치', '반도체']</t>
+          <t>['증시', '외인', '기관']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81200</v>
+        <v>81100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.49%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G11" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="H11" t="n">
         <v>22.59</v>
@@ -1438,7 +1438,7 @@
         <v>22.56</v>
       </c>
       <c r="O11" t="n">
-        <v>121040850850</v>
+        <v>122821684850</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1483,123 +1483,123 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17590</v>
+        <v>238500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.90%</t>
+          <t>'-1.04%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="G12" t="n">
-        <v>275</v>
+        <v>817</v>
       </c>
       <c r="H12" t="n">
-        <v>9.5</v>
+        <v>4.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17750</v>
+        <v>241000</v>
       </c>
       <c r="K12" t="n">
-        <v>17970</v>
+        <v>253000</v>
       </c>
       <c r="L12" t="n">
-        <v>18030</v>
+        <v>257000</v>
       </c>
       <c r="M12" t="n">
-        <v>17420</v>
+        <v>233500</v>
       </c>
       <c r="N12" t="n">
-        <v>9.390000000000001</v>
+        <v>4.08</v>
       </c>
       <c r="O12" t="n">
-        <v>40376326950</v>
+        <v>79090076250</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>1233000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>120000</v>
       </c>
       <c r="R12" t="n">
-        <v>-177000</v>
+        <v>-49000</v>
       </c>
       <c r="S12" t="n">
-        <v>-36000</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>올해 수주 목표 27조 및 미국 원전 건설 관련 긍정적 분위기 언급. 싱가포르 수상 및 미국 원전 수주 기대감. 주주들에게 호소하는 내용 다수 포함.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 아일리아 성과 기반 미래 성장 기대. 외인 공매도 숏커버링으로 인한 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '원전', '건설']</t>
+          <t>['L/O', '아일리아', '경구용 인슐린']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13180</v>
+        <v>17510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.57%</t>
+          <t>'-1.35%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>77</v>
+        <v>288</v>
       </c>
       <c r="H13" t="n">
-        <v>3.18</v>
+        <v>9.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13390</v>
+        <v>17750</v>
       </c>
       <c r="K13" t="n">
-        <v>13770</v>
+        <v>17970</v>
       </c>
       <c r="L13" t="n">
-        <v>13830</v>
+        <v>18030</v>
       </c>
       <c r="M13" t="n">
-        <v>13080</v>
+        <v>17420</v>
       </c>
       <c r="N13" t="n">
-        <v>3.12</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>24197139960</v>
+        <v>41057191695</v>
       </c>
       <c r="P13" t="n">
-        <v>20300</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>3020</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-292000</v>
+        <v>-177000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>올해 수주 목표 27조 및 미국 원전 건설 관련 긍정적 분위기 언급. 싱가포르 수상 및 미국 원전 수주 기대감. 주주들에게 호소하는 내용 다수 포함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['수주', '원전', '건설']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1742000</v>
+        <v>1746000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="G14" t="n">
-        <v>1595</v>
+        <v>1621</v>
       </c>
       <c r="H14" t="n">
         <v>49.71</v>
@@ -1714,7 +1714,7 @@
         <v>49.76</v>
       </c>
       <c r="O14" t="n">
-        <v>2281203775500</v>
+        <v>2340982065500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>나스닥 하락, 외인 매도, 정치적 이슈 등으로 인한 SK하이닉스 주가 부진에 대한 불만과 공매도 비판.</t>
+          <t>외인 매도세 지속 및 추세선 하향 돌파로 하락세. 정치적 이슈와 연관된 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '외인', '공매도']</t>
+          <t>['외인', '추세선', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,79 +1759,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>236750</v>
+        <v>13160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.76%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>793</v>
+        <v>79</v>
       </c>
       <c r="H15" t="n">
-        <v>4.12</v>
+        <v>3.18</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>241000</v>
+        <v>13390</v>
       </c>
       <c r="K15" t="n">
-        <v>253000</v>
+        <v>13770</v>
       </c>
       <c r="L15" t="n">
-        <v>257000</v>
+        <v>13830</v>
       </c>
       <c r="M15" t="n">
-        <v>233500</v>
+        <v>13080</v>
       </c>
       <c r="N15" t="n">
-        <v>4.08</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>77440067250</v>
+        <v>24380177805</v>
       </c>
       <c r="P15" t="n">
-        <v>1233000</v>
+        <v>20300</v>
       </c>
       <c r="Q15" t="n">
-        <v>120000</v>
+        <v>3020</v>
       </c>
       <c r="R15" t="n">
-        <v>-49000</v>
+        <v>-292000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다, 독일 임상 결과 발표 기대감으로 인한 삼천당제약 주가 상승 전망.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['인슐린', 'L/O', '임상']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18100</v>
+        <v>18090</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.37%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>109</v>
       </c>
       <c r="G16" t="n">
-        <v>868</v>
+        <v>904</v>
       </c>
       <c r="H16" t="n">
         <v>4.92</v>
@@ -1898,7 +1898,7 @@
         <v>3.81</v>
       </c>
       <c r="O16" t="n">
-        <v>259117907210</v>
+        <v>260021038580</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 언급에 따른 기대감과 외국인 매도에 대한 우려가 공존.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 지지 언급으로 강세 전망. 외인 매도에도 불구하고 2만원 안착 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '미국증시', '외국인']</t>
+          <t>['광통신', '미국 증시', '외인']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6780</v>
+        <v>6790</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-2.72%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.77</v>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H17" t="n">
         <v>1.1</v>
@@ -1990,7 +1990,7 @@
         <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>44228079485</v>
+        <v>44664089870</v>
       </c>
       <c r="P17" t="n">
         <v>11370</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46000</v>
+        <v>45950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.95%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F18" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G18" t="n">
-        <v>1966</v>
+        <v>1990</v>
       </c>
       <c r="H18" t="n">
         <v>14.12</v>
@@ -2082,7 +2082,7 @@
         <v>14.1</v>
       </c>
       <c r="O18" t="n">
-        <v>33281932050</v>
+        <v>33741264225</v>
       </c>
       <c r="P18" t="n">
         <v>69200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 및 2~3조원 매출 기대감으로 인한 HLB 주가 상승 전망.</t>
+          <t>FDA 승인 가능성 90% 이상 전망 및 2~3조원 매출 기대감. 공매도와의 공방 속 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['FDA', '매출', '신약']</t>
+          <t>['FDA', '간암', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12450</v>
+        <v>12430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.30%</t>
+          <t>'-4.46%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1.88</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H19" t="n">
         <v>1.42</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>34784753550</v>
+        <v>35191260165</v>
       </c>
       <c r="P19" t="n">
         <v>22250</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30150</v>
+        <v>30250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.04%</t>
+          <t>'-4.72%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="H20" t="n">
         <v>10.78</v>
@@ -2266,7 +2266,7 @@
         <v>10.77</v>
       </c>
       <c r="O20" t="n">
-        <v>83886011375</v>
+        <v>84718707125</v>
       </c>
       <c r="P20" t="n">
         <v>75900</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>경쟁사 대비 저조한 주가 흐름 및 급락세에 대한 불만 표출. 단기 반등 기대감과 함께 부정적 전망.</t>
+          <t>가온전선과의 비교 열세 속 하한가 근접, 외인 및 프로그램 매도세 지속. "쪽박전선" 비난.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가', '급락', '주포']</t>
+          <t>['주가', '기관', '외인']</t>
         </is>
       </c>
       <c r="X20" t="n">
